--- a/Input/Verleiherabgaben.xlsx
+++ b/Input/Verleiherabgaben.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kinoklub\Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\R Packages\Kinoklub\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7B8AE6-FEC6-4190-B050-D8583149A9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735DFE3D-DA3C-4449-AF08-2933BE7BA622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6720" yWindow="3180" windowWidth="15684" windowHeight="11832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Verleiherabgaben" sheetId="1" r:id="rId1"/>
@@ -498,7 +498,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{EB39806D-A340-4E6B-8E59-89A25516E3F2}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
     <dxf>
@@ -962,21 +962,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="61.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="39" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="43" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1002,7 +1002,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>45667</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45674</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45676</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45682</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45683</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45689</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45690</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45690</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45695</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45701</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>45738</v>
       </c>
@@ -1253,7 +1253,7 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5BD6C4FD-BF72-41F7-85FD-AAAD92F80620}">
           <x14:formula1>
             <xm:f>'Kinoförderer gratis'!$A$2:$A$23</xm:f>
@@ -1264,7 +1264,7 @@
           <x14:formula1>
             <xm:f>'Kinoförderer gratis'!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H12</xm:sqref>
+          <xm:sqref>H1:H1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1275,16 +1275,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2012A76-D168-4BE0-9450-2E40BA8CE7CD}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.33203125" customWidth="1"/>
+    <col min="1" max="1" width="43.28515625" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>52</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>51</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>18</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>12</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>72</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>74</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>77</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>78</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>85</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>87</v>
       </c>
@@ -1709,16 +1709,16 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="9"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="9"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="9"/>
     </row>
   </sheetData>
@@ -1745,22 +1745,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB792523-3058-487E-914C-DA84AFB7228F}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>

--- a/Input/Verleiherabgaben.xlsx
+++ b/Input/Verleiherabgaben.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kinoklub\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7B8AE6-FEC6-4190-B050-D8583149A9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2676C321-F49C-45DA-B3EA-7CCA2A850092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6720" yWindow="3180" windowWidth="15684" windowHeight="11832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="14580" windowHeight="17370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Verleiherabgaben" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="127">
   <si>
     <t>Datum</t>
   </si>
@@ -380,6 +380,45 @@
   </si>
   <si>
     <t>Suisanummer</t>
+  </si>
+  <si>
+    <t>1021.270</t>
+  </si>
+  <si>
+    <t>Universal Pictures International switzerland GmbH</t>
+  </si>
+  <si>
+    <t>Mühlebachstrasse 54</t>
+  </si>
+  <si>
+    <t>The Brutalist</t>
+  </si>
+  <si>
+    <t>The wild Robot</t>
+  </si>
+  <si>
+    <t>Prisoners of Fate</t>
+  </si>
+  <si>
+    <t>Antarctica Calling</t>
+  </si>
+  <si>
+    <t>Emilia Perez</t>
+  </si>
+  <si>
+    <t>1019.964</t>
+  </si>
+  <si>
+    <t>The substance</t>
+  </si>
+  <si>
+    <t>1020.928</t>
+  </si>
+  <si>
+    <t>1018.767</t>
+  </si>
+  <si>
+    <t>1018.950</t>
   </si>
 </sst>
 </file>
@@ -474,7 +513,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -495,6 +534,7 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{EB39806D-A340-4E6B-8E59-89A25516E3F2}"/>
@@ -652,8 +692,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0FB193BD-2953-40BE-9E24-FED98BF5CDC0}" name="Table3" displayName="Table3" ref="A1:H12" totalsRowShown="0">
-  <autoFilter ref="A1:H12" xr:uid="{0FB193BD-2953-40BE-9E24-FED98BF5CDC0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0FB193BD-2953-40BE-9E24-FED98BF5CDC0}" name="Table3" displayName="Table3" ref="A1:H18" totalsRowShown="0">
+  <autoFilter ref="A1:H18" xr:uid="{0FB193BD-2953-40BE-9E24-FED98BF5CDC0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H12">
     <sortCondition ref="A1:A12"/>
   </sortState>
@@ -672,8 +712,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{41B7D794-AABB-4EC4-84C2-1A317703EE4E}" name="Table1" displayName="Table1" ref="A1:E25" totalsRowShown="0" dataDxfId="5">
-  <autoFilter ref="A1:E25" xr:uid="{41B7D794-AABB-4EC4-84C2-1A317703EE4E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{41B7D794-AABB-4EC4-84C2-1A317703EE4E}" name="Table1" displayName="Table1" ref="A1:E26" totalsRowShown="0" dataDxfId="5">
+  <autoFilter ref="A1:E26" xr:uid="{41B7D794-AABB-4EC4-84C2-1A317703EE4E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A19">
     <sortCondition ref="A1:A51"/>
   </sortState>
@@ -961,22 +1001,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="61.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.6328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="39" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="43" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1002,7 +1042,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>45667</v>
       </c>
@@ -1023,7 +1063,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>45674</v>
       </c>
@@ -1045,7 +1085,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>45676</v>
       </c>
@@ -1067,7 +1107,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>45682</v>
       </c>
@@ -1089,7 +1129,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>45683</v>
       </c>
@@ -1111,7 +1151,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>45689</v>
       </c>
@@ -1133,7 +1173,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>45690</v>
       </c>
@@ -1155,7 +1195,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>45690</v>
       </c>
@@ -1177,7 +1217,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>45695</v>
       </c>
@@ -1199,7 +1239,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>45701</v>
       </c>
@@ -1221,7 +1261,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>45738</v>
       </c>
@@ -1241,6 +1281,132 @@
       </c>
       <c r="H12" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>45718</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" s="5">
+        <v>150</v>
+      </c>
+      <c r="E13">
+        <v>30</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>45903</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="5">
+        <v>150</v>
+      </c>
+      <c r="E14">
+        <v>30</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>45738</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="5">
+        <v>150</v>
+      </c>
+      <c r="E15">
+        <v>30</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>45739</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="5">
+        <v>150</v>
+      </c>
+      <c r="E16">
+        <v>30</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>45745</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="5">
+        <v>150</v>
+      </c>
+      <c r="E17">
+        <v>30</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>45731</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="5">
+        <v>150</v>
+      </c>
+      <c r="E18">
+        <v>30</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1253,7 +1419,7 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5BD6C4FD-BF72-41F7-85FD-AAAD92F80620}">
           <x14:formula1>
             <xm:f>'Kinoförderer gratis'!$A$2:$A$23</xm:f>
@@ -1264,7 +1430,7 @@
           <x14:formula1>
             <xm:f>'Kinoförderer gratis'!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H12</xm:sqref>
+          <xm:sqref>H2:H18</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1275,16 +1441,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2012A76-D168-4BE0-9450-2E40BA8CE7CD}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.33203125" customWidth="1"/>
+    <col min="1" max="1" width="43.36328125" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.90625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1301,7 +1467,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
@@ -1318,7 +1484,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -1335,7 +1501,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -1352,7 +1518,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>52</v>
       </c>
@@ -1369,7 +1535,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -1386,7 +1552,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -1403,7 +1569,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -1420,7 +1586,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1437,7 +1603,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>51</v>
       </c>
@@ -1454,7 +1620,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
@@ -1471,7 +1637,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
@@ -1488,7 +1654,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>18</v>
       </c>
@@ -1505,7 +1671,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
@@ -1522,7 +1688,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
@@ -1539,7 +1705,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
@@ -1556,7 +1722,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
@@ -1573,7 +1739,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1590,7 +1756,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>12</v>
       </c>
@@ -1607,7 +1773,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>72</v>
       </c>
@@ -1624,7 +1790,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>74</v>
       </c>
@@ -1641,7 +1807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>77</v>
       </c>
@@ -1658,7 +1824,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>78</v>
       </c>
@@ -1675,7 +1841,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>85</v>
       </c>
@@ -1692,7 +1858,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>87</v>
       </c>
@@ -1709,16 +1875,33 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="26" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="9"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="9"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="9"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="9"/>
     </row>
   </sheetData>
@@ -1745,22 +1928,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB792523-3058-487E-914C-DA84AFB7228F}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>

--- a/Input/Verleiherabgaben.xlsx
+++ b/Input/Verleiherabgaben.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kinoklub\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2676C321-F49C-45DA-B3EA-7CCA2A850092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21EA47D-86C7-4C8C-8801-761C470DE473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="14580" windowHeight="17370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Verleiherabgaben" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="157">
   <si>
     <t>Datum</t>
   </si>
@@ -373,9 +373,6 @@
     <t>Die Witwe Clicquot</t>
   </si>
   <si>
-    <t>Gefangene des Schicksals (Zusammenarbeit mit Impuls Zusammenleben)</t>
-  </si>
-  <si>
     <t>1020.428</t>
   </si>
   <si>
@@ -419,6 +416,99 @@
   </si>
   <si>
     <t>1018.950</t>
+  </si>
+  <si>
+    <t>1020.059</t>
+  </si>
+  <si>
+    <t>1020.846</t>
+  </si>
+  <si>
+    <t>1018.952</t>
+  </si>
+  <si>
+    <t>1019.535</t>
+  </si>
+  <si>
+    <t>1021.875</t>
+  </si>
+  <si>
+    <t>1010.858</t>
+  </si>
+  <si>
+    <t>1020.294</t>
+  </si>
+  <si>
+    <t>1021.021</t>
+  </si>
+  <si>
+    <t>1018.390</t>
+  </si>
+  <si>
+    <t>1020.744</t>
+  </si>
+  <si>
+    <t>1020.176</t>
+  </si>
+  <si>
+    <t>1020.835</t>
+  </si>
+  <si>
+    <t>Heldin</t>
+  </si>
+  <si>
+    <t>Wir erben</t>
+  </si>
+  <si>
+    <t>Sauvages</t>
+  </si>
+  <si>
+    <t>Wunderschöner</t>
+  </si>
+  <si>
+    <t>Friedas Fall</t>
+  </si>
+  <si>
+    <t>Das Licht</t>
+  </si>
+  <si>
+    <t>DenkAnstoss: Mutters Atelier</t>
+  </si>
+  <si>
+    <t>An - Von Kirschblüten und roten Bohnen</t>
+  </si>
+  <si>
+    <t>Paddington in Peru</t>
+  </si>
+  <si>
+    <t>On Becoming a Guinea Fowl</t>
+  </si>
+  <si>
+    <t>Sidonie au Japon</t>
+  </si>
+  <si>
+    <t>Ein Mädchen namens Willow</t>
+  </si>
+  <si>
+    <t>Niki</t>
+  </si>
+  <si>
+    <t>Un Ours dans le Jura</t>
+  </si>
+  <si>
+    <t>JMH Distributions SA</t>
+  </si>
+  <si>
+    <t>Promenade 13</t>
+  </si>
+  <si>
+    <t>2316</t>
+  </si>
+  <si>
+    <t>Les Ponts-de-Martel</t>
+  </si>
+  <si>
+    <t>1018.523</t>
   </si>
 </sst>
 </file>
@@ -513,7 +603,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -534,7 +624,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{EB39806D-A340-4E6B-8E59-89A25516E3F2}"/>
@@ -692,10 +781,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0FB193BD-2953-40BE-9E24-FED98BF5CDC0}" name="Table3" displayName="Table3" ref="A1:H18" totalsRowShown="0">
-  <autoFilter ref="A1:H18" xr:uid="{0FB193BD-2953-40BE-9E24-FED98BF5CDC0}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H12">
-    <sortCondition ref="A1:A12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0FB193BD-2953-40BE-9E24-FED98BF5CDC0}" name="Table3" displayName="Table3" ref="A1:H32" totalsRowShown="0">
+  <autoFilter ref="A1:H32" xr:uid="{0FB193BD-2953-40BE-9E24-FED98BF5CDC0}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H17">
+    <sortCondition ref="A1:A17"/>
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{DBD88967-C196-46D7-A0F4-D1ABEE204E92}" name="Datum" dataDxfId="11"/>
@@ -712,8 +801,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{41B7D794-AABB-4EC4-84C2-1A317703EE4E}" name="Table1" displayName="Table1" ref="A1:E26" totalsRowShown="0" dataDxfId="5">
-  <autoFilter ref="A1:E26" xr:uid="{41B7D794-AABB-4EC4-84C2-1A317703EE4E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{41B7D794-AABB-4EC4-84C2-1A317703EE4E}" name="Table1" displayName="Table1" ref="A1:E27" totalsRowShown="0" dataDxfId="5">
+  <autoFilter ref="A1:E27" xr:uid="{41B7D794-AABB-4EC4-84C2-1A317703EE4E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A19">
     <sortCondition ref="A1:A51"/>
   </sortState>
@@ -1001,7 +1090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.453125" customWidth="1"/>
@@ -1024,7 +1113,7 @@
         <v>83</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>25</v>
@@ -1157,7 +1246,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D7" s="5">
         <v>0</v>
@@ -1200,7 +1289,7 @@
         <v>45690</v>
       </c>
       <c r="B9" s="8"/>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D9" s="5">
@@ -1263,66 +1352,65 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>45738</v>
+        <v>45718</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="1" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="D12" s="5">
         <v>150</v>
       </c>
-      <c r="E12" s="7">
-        <v>30</v>
-      </c>
-      <c r="F12"/>
+      <c r="E12">
+        <v>30</v>
+      </c>
       <c r="G12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H12" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
-        <v>45718</v>
+        <v>45725</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="5">
+        <v>150</v>
+      </c>
+      <c r="E13">
+        <v>30</v>
+      </c>
+      <c r="G13" t="s">
+        <v>117</v>
+      </c>
+      <c r="H13" t="s">
         <v>114</v>
-      </c>
-      <c r="D13" s="5">
-        <v>150</v>
-      </c>
-      <c r="E13">
-        <v>30</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
-        <v>45903</v>
+        <v>45731</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="5">
+        <v>50</v>
+      </c>
+      <c r="E14">
+        <v>30</v>
+      </c>
+      <c r="G14" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="5">
-        <v>150</v>
-      </c>
-      <c r="E14">
-        <v>30</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>115</v>
+      <c r="H14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1339,10 +1427,10 @@
       <c r="E15">
         <v>30</v>
       </c>
-      <c r="G15" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="H15" s="12" t="s">
+      <c r="G15" t="s">
+        <v>118</v>
+      </c>
+      <c r="H15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1352,7 +1440,7 @@
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16" s="5">
         <v>150</v>
@@ -1360,10 +1448,10 @@
       <c r="E16">
         <v>30</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="12" t="s">
+      <c r="G16" t="s">
+        <v>119</v>
+      </c>
+      <c r="H16" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1373,7 +1461,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D17" s="5">
         <v>150</v>
@@ -1381,20 +1469,20 @@
       <c r="E17">
         <v>30</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="H17" s="12" t="s">
+      <c r="G17" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>45731</v>
+        <v>45750</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D18" s="5">
         <v>150</v>
@@ -1402,11 +1490,302 @@
       <c r="E18">
         <v>30</v>
       </c>
-      <c r="G18" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="H18" s="12" t="s">
+      <c r="G18" t="s">
+        <v>138</v>
+      </c>
+      <c r="H18" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <v>45753</v>
+      </c>
+      <c r="B19" s="8"/>
+      <c r="C19" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="5">
+        <v>150</v>
+      </c>
+      <c r="E19">
+        <v>30</v>
+      </c>
+      <c r="G19" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>45753</v>
+      </c>
+      <c r="B20" s="8"/>
+      <c r="C20" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="5">
+        <v>150</v>
+      </c>
+      <c r="E20">
+        <v>30</v>
+      </c>
+      <c r="G20" t="s">
+        <v>140</v>
+      </c>
+      <c r="H20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>45757</v>
+      </c>
+      <c r="B21" s="8"/>
+      <c r="C21" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" s="5">
+        <v>150</v>
+      </c>
+      <c r="E21">
+        <v>30</v>
+      </c>
+      <c r="G21" t="s">
+        <v>138</v>
+      </c>
+      <c r="H21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>45758</v>
+      </c>
+      <c r="B22" s="8"/>
+      <c r="C22" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="5">
+        <v>190</v>
+      </c>
+      <c r="E22">
+        <v>30</v>
+      </c>
+      <c r="G22" t="s">
+        <v>141</v>
+      </c>
+      <c r="H22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
+        <v>45760</v>
+      </c>
+      <c r="B23" s="8"/>
+      <c r="C23" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" s="5">
+        <v>150</v>
+      </c>
+      <c r="E23">
+        <v>30</v>
+      </c>
+      <c r="G23" t="s">
+        <v>142</v>
+      </c>
+      <c r="H23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>45766</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="5">
+        <v>150</v>
+      </c>
+      <c r="E24">
+        <v>30</v>
+      </c>
+      <c r="G24" t="s">
+        <v>143</v>
+      </c>
+      <c r="H24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
+        <v>45773</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="D25" s="5">
+        <v>150</v>
+      </c>
+      <c r="E25">
+        <v>30</v>
+      </c>
+      <c r="G25" t="s">
+        <v>144</v>
+      </c>
+      <c r="H25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>45781</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="5">
+        <v>150</v>
+      </c>
+      <c r="E26">
+        <v>30</v>
+      </c>
+      <c r="G26" t="s">
+        <v>145</v>
+      </c>
+      <c r="H26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>45781</v>
+      </c>
+      <c r="B27" s="8"/>
+      <c r="C27" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="5">
+        <v>150</v>
+      </c>
+      <c r="E27">
+        <v>30</v>
+      </c>
+      <c r="G27" t="s">
+        <v>146</v>
+      </c>
+      <c r="H27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>45787</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" s="5">
+        <v>150</v>
+      </c>
+      <c r="E28">
+        <v>30</v>
+      </c>
+      <c r="G28" t="s">
+        <v>147</v>
+      </c>
+      <c r="H28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
+        <v>45793</v>
+      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="5">
+        <v>150</v>
+      </c>
+      <c r="E29">
+        <v>30</v>
+      </c>
+      <c r="G29" t="s">
+        <v>148</v>
+      </c>
+      <c r="H29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>45795</v>
+      </c>
+      <c r="B30" s="8"/>
+      <c r="C30" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D30" s="5">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>30</v>
+      </c>
+      <c r="G30" t="s">
+        <v>149</v>
+      </c>
+      <c r="H30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
+        <v>45801</v>
+      </c>
+      <c r="B31" s="8"/>
+      <c r="C31" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D31" s="5">
+        <v>150</v>
+      </c>
+      <c r="E31">
+        <v>30</v>
+      </c>
+      <c r="G31" t="s">
+        <v>150</v>
+      </c>
+      <c r="H31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
+        <v>45807</v>
+      </c>
+      <c r="B32" s="8"/>
+      <c r="C32" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D32" s="5">
+        <v>150</v>
+      </c>
+      <c r="E32">
+        <v>30</v>
+      </c>
+      <c r="G32" t="s">
+        <v>151</v>
+      </c>
+      <c r="H32" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -1424,13 +1803,13 @@
           <x14:formula1>
             <xm:f>'Kinoförderer gratis'!$A$2:$A$23</xm:f>
           </x14:formula1>
-          <xm:sqref>I13:I262</xm:sqref>
+          <xm:sqref>I12:I261</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{80937494-2B0B-4CA6-82E1-990B543FC73E}">
           <x14:formula1>
             <xm:f>'Kinoförderer gratis'!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H18</xm:sqref>
+          <xm:sqref>H2:H32</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1877,19 +2256,36 @@
     </row>
     <row r="26" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>34</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="26" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">

--- a/Input/Verleiherabgaben.xlsx
+++ b/Input/Verleiherabgaben.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kinoklub\Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\R Packages\Kinoklub\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21EA47D-86C7-4C8C-8801-761C470DE473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E9E70C-41CE-46A6-B6E4-08461F2D6364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Verleiherabgaben" sheetId="1" r:id="rId1"/>
@@ -627,7 +627,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{EB39806D-A340-4E6B-8E59-89A25516E3F2}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
     <dxf>
@@ -1091,21 +1091,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.453125" customWidth="1"/>
-    <col min="2" max="2" width="12.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.36328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="61.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="39" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="48.7109375" customWidth="1"/>
     <col min="9" max="9" width="43" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>45667</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45674</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45676</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45682</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45683</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45689</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45690</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45690</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45695</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45701</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>45718</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45725</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>45731</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>45738</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>45739</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>45745</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>45750</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>45753</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>45753</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>45757</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>45758</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>45760</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>45766</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>45773</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>45781</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>45781</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>45787</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>45793</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>45795</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>45801</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>45807</v>
       </c>
@@ -1820,16 +1820,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2012A76-D168-4BE0-9450-2E40BA8CE7CD}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.36328125" customWidth="1"/>
+    <col min="1" max="1" width="43.42578125" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="26" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>52</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="26" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>51</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="26" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>18</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="26" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="26" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>8</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>12</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>72</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>74</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>77</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>78</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>85</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>87</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="26" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>114</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="26" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>152</v>
       </c>
@@ -2288,16 +2288,16 @@
         <v>155</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="9"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="9"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="9"/>
     </row>
   </sheetData>
@@ -2324,22 +2324,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB792523-3058-487E-914C-DA84AFB7228F}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6328125" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>

--- a/Input/Verleiherabgaben.xlsx
+++ b/Input/Verleiherabgaben.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\R Packages\Kinoklub\Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kinoklub\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E9E70C-41CE-46A6-B6E4-08461F2D6364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44088841-7765-48E2-8939-AA06D953F0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="14580" windowHeight="17370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Verleiherabgaben" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="158">
   <si>
     <t>Datum</t>
   </si>
@@ -509,6 +509,9 @@
   </si>
   <si>
     <t>1018.523</t>
+  </si>
+  <si>
+    <t>SC02.675</t>
   </si>
 </sst>
 </file>
@@ -627,7 +630,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{EB39806D-A340-4E6B-8E59-89A25516E3F2}"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
     <dxf>
@@ -1091,21 +1094,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="61.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="48.7109375" customWidth="1"/>
+    <col min="7" max="7" width="61.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="48.7265625" customWidth="1"/>
     <col min="9" max="9" width="43" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1131,7 +1134,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>45667</v>
       </c>
@@ -1152,7 +1155,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>45674</v>
       </c>
@@ -1174,7 +1177,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>45676</v>
       </c>
@@ -1196,7 +1199,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>45682</v>
       </c>
@@ -1218,7 +1221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>45683</v>
       </c>
@@ -1240,7 +1243,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>45689</v>
       </c>
@@ -1262,7 +1265,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>45690</v>
       </c>
@@ -1284,7 +1287,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>45690</v>
       </c>
@@ -1306,7 +1309,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>45695</v>
       </c>
@@ -1328,7 +1331,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>45701</v>
       </c>
@@ -1350,7 +1353,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>45718</v>
       </c>
@@ -1371,7 +1374,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>45725</v>
       </c>
@@ -1392,7 +1395,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>45731</v>
       </c>
@@ -1413,7 +1416,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>45738</v>
       </c>
@@ -1434,7 +1437,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>45739</v>
       </c>
@@ -1455,7 +1458,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>45745</v>
       </c>
@@ -1476,7 +1479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>45750</v>
       </c>
@@ -1497,7 +1500,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>45753</v>
       </c>
@@ -1518,7 +1521,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>45753</v>
       </c>
@@ -1539,7 +1542,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>45757</v>
       </c>
@@ -1560,7 +1563,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>45758</v>
       </c>
@@ -1581,7 +1584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>45760</v>
       </c>
@@ -1602,7 +1605,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>45766</v>
       </c>
@@ -1623,11 +1626,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>45773</v>
       </c>
       <c r="B25" s="8"/>
+      <c r="C25" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="D25" s="5">
         <v>150</v>
       </c>
@@ -1641,7 +1647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>45781</v>
       </c>
@@ -1662,7 +1668,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>45781</v>
       </c>
@@ -1683,7 +1689,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>45787</v>
       </c>
@@ -1704,7 +1710,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>45793</v>
       </c>
@@ -1725,7 +1731,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>45795</v>
       </c>
@@ -1746,7 +1752,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>45801</v>
       </c>
@@ -1767,7 +1773,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>45807</v>
       </c>
@@ -1820,16 +1826,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2012A76-D168-4BE0-9450-2E40BA8CE7CD}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.42578125" customWidth="1"/>
+    <col min="1" max="1" width="43.453125" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1846,7 +1852,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
@@ -1863,7 +1869,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -1880,7 +1886,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -1897,7 +1903,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>52</v>
       </c>
@@ -1914,7 +1920,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -1931,7 +1937,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -1948,7 +1954,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -1965,7 +1971,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1982,7 +1988,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>51</v>
       </c>
@@ -1999,7 +2005,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
@@ -2016,7 +2022,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
@@ -2033,7 +2039,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>18</v>
       </c>
@@ -2050,7 +2056,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
@@ -2067,7 +2073,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
@@ -2084,7 +2090,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
@@ -2101,7 +2107,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
@@ -2118,7 +2124,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>8</v>
       </c>
@@ -2135,7 +2141,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>12</v>
       </c>
@@ -2152,7 +2158,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>72</v>
       </c>
@@ -2169,7 +2175,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>74</v>
       </c>
@@ -2186,7 +2192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>77</v>
       </c>
@@ -2203,7 +2209,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>78</v>
       </c>
@@ -2220,7 +2226,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>85</v>
       </c>
@@ -2237,7 +2243,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>87</v>
       </c>
@@ -2254,7 +2260,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>114</v>
       </c>
@@ -2271,7 +2277,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>152</v>
       </c>
@@ -2288,16 +2294,16 @@
         <v>155</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="9"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="9"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="9"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="9"/>
     </row>
   </sheetData>
@@ -2324,22 +2330,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB792523-3058-487E-914C-DA84AFB7228F}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
